--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="27">
   <si>
     <t>Docente</t>
   </si>
@@ -75,24 +75,6 @@
     <t>2BLCM</t>
   </si>
   <si>
-    <t>6AEM</t>
-  </si>
-  <si>
-    <t>6ALCM</t>
-  </si>
-  <si>
-    <t>6APM</t>
-  </si>
-  <si>
-    <t>6ARHM</t>
-  </si>
-  <si>
-    <t>6BEM</t>
-  </si>
-  <si>
-    <t>6BLCM</t>
-  </si>
-  <si>
     <t>2ALCM</t>
   </si>
   <si>
@@ -115,9 +97,6 @@
   </si>
   <si>
     <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA II</t>
-  </si>
-  <si>
-    <t>LITERATURA</t>
   </si>
 </sst>
 </file>
@@ -481,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -534,7 +513,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>34</v>
@@ -569,7 +548,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>39</v>
@@ -604,7 +583,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>40</v>
@@ -639,7 +618,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -668,382 +647,247 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>88.37</v>
+      </c>
+      <c r="H6" s="1">
+        <v>11.63</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.6</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>83.78</v>
+      </c>
+      <c r="H7" s="1">
+        <v>16.22</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.7</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <v>26.67</v>
+      </c>
+      <c r="H8" s="1">
+        <v>73.33</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.5</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G9" s="1">
+        <v>70.97</v>
+      </c>
+      <c r="H9" s="1">
+        <v>29.03</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.9</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>41</v>
+      </c>
+      <c r="E10">
         <v>33</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="H10" s="1">
+        <v>19.51</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G11" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>88.37</v>
+        <v>93.94</v>
       </c>
       <c r="H12" s="1">
-        <v>11.63</v>
+        <v>6.06</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13">
-        <v>37</v>
-      </c>
-      <c r="E13">
-        <v>31</v>
-      </c>
-      <c r="F13">
-        <v>6</v>
-      </c>
-      <c r="G13" s="1">
-        <v>83.78</v>
-      </c>
-      <c r="H13" s="1">
-        <v>16.22</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14">
-        <v>30</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-      <c r="F14">
-        <v>22</v>
-      </c>
-      <c r="G14" s="1">
-        <v>26.67</v>
-      </c>
-      <c r="H14" s="1">
-        <v>73.33</v>
-      </c>
-      <c r="I14" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>31</v>
-      </c>
-      <c r="E15">
-        <v>22</v>
-      </c>
-      <c r="F15">
-        <v>9</v>
-      </c>
-      <c r="G15" s="1">
-        <v>70.97</v>
-      </c>
-      <c r="H15" s="1">
-        <v>29.03</v>
-      </c>
-      <c r="I15" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
-      <c r="K15" s="1">
-        <v>22.58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16">
-        <v>41</v>
-      </c>
-      <c r="E16">
-        <v>33</v>
-      </c>
-      <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="G16" s="1">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="H16" s="1">
-        <v>19.51</v>
-      </c>
-      <c r="I16" s="2">
-        <v>7</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17">
-        <v>32</v>
-      </c>
-      <c r="E17">
-        <v>28</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H17" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18">
-        <v>33</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>33</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>100</v>
-      </c>
-      <c r="J18">
-        <v>33</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1053,7 +897,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1106,7 +950,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>34</v>
@@ -1138,7 +982,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>39</v>
@@ -1170,7 +1014,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>40</v>
@@ -1202,7 +1046,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -1228,160 +1072,214 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>41</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1390,201 +1288,9 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13">
-        <v>37</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>37</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>100</v>
-      </c>
-      <c r="J13">
-        <v>37</v>
-      </c>
-      <c r="K13" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14">
-        <v>30</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>30</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>100</v>
-      </c>
-      <c r="J14">
-        <v>30</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>31</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>31</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
-      </c>
-      <c r="J15">
-        <v>31</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16">
-        <v>41</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>41</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>41</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17">
-        <v>32</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>32</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>100</v>
-      </c>
-      <c r="J17">
-        <v>32</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18">
-        <v>33</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>33</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>100</v>
-      </c>
-      <c r="J18">
-        <v>33</v>
-      </c>
-      <c r="K18" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1595,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1648,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>34</v>
@@ -1683,7 +1389,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>39</v>
@@ -1718,7 +1424,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>40</v>
@@ -1753,7 +1459,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>41</v>
@@ -1782,382 +1488,247 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>88.37</v>
+      </c>
+      <c r="H6" s="1">
+        <v>11.63</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.6</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>83.78</v>
+      </c>
+      <c r="H7" s="1">
+        <v>16.22</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.7</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <v>26.67</v>
+      </c>
+      <c r="H8" s="1">
+        <v>73.33</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5.5</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G9" s="1">
+        <v>70.97</v>
+      </c>
+      <c r="H9" s="1">
+        <v>29.03</v>
+      </c>
+      <c r="I9" s="2">
+        <v>6.9</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10">
+        <v>41</v>
+      </c>
+      <c r="E10">
         <v>33</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="H10" s="1">
+        <v>19.51</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G11" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.3</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>88.37</v>
+        <v>93.94</v>
       </c>
       <c r="H12" s="1">
-        <v>11.63</v>
+        <v>6.06</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13">
-        <v>37</v>
-      </c>
-      <c r="E13">
-        <v>31</v>
-      </c>
-      <c r="F13">
-        <v>6</v>
-      </c>
-      <c r="G13" s="1">
-        <v>83.78</v>
-      </c>
-      <c r="H13" s="1">
-        <v>16.22</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14">
-        <v>30</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-      <c r="F14">
-        <v>22</v>
-      </c>
-      <c r="G14" s="1">
-        <v>26.67</v>
-      </c>
-      <c r="H14" s="1">
-        <v>73.33</v>
-      </c>
-      <c r="I14" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>31</v>
-      </c>
-      <c r="E15">
-        <v>22</v>
-      </c>
-      <c r="F15">
-        <v>9</v>
-      </c>
-      <c r="G15" s="1">
-        <v>70.97</v>
-      </c>
-      <c r="H15" s="1">
-        <v>29.03</v>
-      </c>
-      <c r="I15" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="J15">
-        <v>7</v>
-      </c>
-      <c r="K15" s="1">
-        <v>22.58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16">
-        <v>41</v>
-      </c>
-      <c r="E16">
-        <v>33</v>
-      </c>
-      <c r="F16">
-        <v>8</v>
-      </c>
-      <c r="G16" s="1">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="H16" s="1">
-        <v>19.51</v>
-      </c>
-      <c r="I16" s="2">
-        <v>7</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17">
-        <v>32</v>
-      </c>
-      <c r="E17">
-        <v>28</v>
-      </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H17" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="I17" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18">
-        <v>33</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>33</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>100</v>
-      </c>
-      <c r="J18">
-        <v>33</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -51,46 +51,46 @@
     <t>Por_Blan</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
     <t>2AEM</t>
   </si>
   <si>
+    <t>2BLCM</t>
+  </si>
+  <si>
+    <t>2APV</t>
+  </si>
+  <si>
+    <t>2AEV</t>
+  </si>
+  <si>
+    <t>2ALCV</t>
+  </si>
+  <si>
+    <t>2ARHV</t>
+  </si>
+  <si>
+    <t>2ALCM</t>
+  </si>
+  <si>
     <t>2APM</t>
   </si>
   <si>
     <t>2ARHM</t>
   </si>
   <si>
-    <t>2BLCM</t>
-  </si>
-  <si>
-    <t>2ALCM</t>
-  </si>
-  <si>
     <t>2BEM</t>
-  </si>
-  <si>
-    <t>2APV</t>
-  </si>
-  <si>
-    <t>2AEV</t>
-  </si>
-  <si>
-    <t>2ALCV</t>
-  </si>
-  <si>
-    <t>2ARHV</t>
   </si>
   <si>
     <t>2ASV</t>
@@ -551,22 +551,22 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>94.87</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>5.13</v>
+        <v>34.15</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -586,22 +586,22 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>85</v>
+        <v>26.67</v>
       </c>
       <c r="H4" s="1">
-        <v>15</v>
+        <v>73.33</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -612,7 +612,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -621,22 +621,22 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>65.84999999999999</v>
+        <v>70.97</v>
       </c>
       <c r="H5" s="1">
-        <v>34.15</v>
+        <v>29.03</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -656,22 +656,22 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>88.37</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>11.63</v>
+        <v>19.51</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -691,22 +691,22 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>83.78</v>
+        <v>87.5</v>
       </c>
       <c r="H7" s="1">
-        <v>16.22</v>
+        <v>12.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
@@ -726,22 +726,22 @@
         <v>26</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>26.67</v>
+        <v>88.37</v>
       </c>
       <c r="H8" s="1">
-        <v>73.33</v>
+        <v>11.63</v>
       </c>
       <c r="I8" s="2">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -761,22 +761,22 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>70.97</v>
+        <v>94.87</v>
       </c>
       <c r="H9" s="1">
-        <v>29.03</v>
+        <v>5.13</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -796,22 +796,22 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>80.48999999999999</v>
+        <v>85</v>
       </c>
       <c r="H10" s="1">
-        <v>19.51</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -831,22 +831,22 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>83.78</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>16.22</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1000,7 +1000,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1017,13 +1017,13 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -1049,13 +1049,13 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1081,13 +1081,13 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -1113,13 +1113,13 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
@@ -1145,13 +1145,13 @@
         <v>26</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1177,13 +1177,13 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1192,7 +1192,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1209,13 +1209,13 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1241,13 +1241,13 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1392,22 +1392,22 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>94.87</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>5.13</v>
+        <v>34.15</v>
       </c>
       <c r="I3" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1427,22 +1427,22 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>85</v>
+        <v>26.67</v>
       </c>
       <c r="H4" s="1">
-        <v>15</v>
+        <v>73.33</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -1462,22 +1462,22 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>65.84999999999999</v>
+        <v>70.97</v>
       </c>
       <c r="H5" s="1">
-        <v>34.15</v>
+        <v>29.03</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1497,22 +1497,22 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>88.37</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>11.63</v>
+        <v>19.51</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1532,22 +1532,22 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>83.78</v>
+        <v>87.5</v>
       </c>
       <c r="H7" s="1">
-        <v>16.22</v>
+        <v>12.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
@@ -1567,22 +1567,22 @@
         <v>26</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>26.67</v>
+        <v>88.37</v>
       </c>
       <c r="H8" s="1">
-        <v>73.33</v>
+        <v>11.63</v>
       </c>
       <c r="I8" s="2">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1602,22 +1602,22 @@
         <v>26</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>70.97</v>
+        <v>94.87</v>
       </c>
       <c r="H9" s="1">
-        <v>29.03</v>
+        <v>5.13</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1637,22 +1637,22 @@
         <v>26</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>80.48999999999999</v>
+        <v>85</v>
       </c>
       <c r="H10" s="1">
-        <v>19.51</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1672,22 +1672,22 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>87.5</v>
+        <v>83.78</v>
       </c>
       <c r="H11" s="1">
-        <v>12.5</v>
+        <v>16.22</v>
       </c>
       <c r="I11" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="28">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Hernández Mendoza Delfina</t>
@@ -63,6 +62,12 @@
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA II</t>
+  </si>
+  <si>
     <t>2AEM</t>
   </si>
   <si>
@@ -94,9 +99,6 @@
   </si>
   <si>
     <t>2ASV</t>
-  </si>
-  <si>
-    <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA II</t>
   </si>
 </sst>
 </file>
@@ -460,11 +462,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -510,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>34</v>
@@ -525,10 +527,10 @@
         <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>73.53</v>
+        <v>73.5</v>
       </c>
       <c r="H2" s="1">
-        <v>26.47</v>
+        <v>26.5</v>
       </c>
       <c r="I2" s="2">
         <v>6.9</v>
@@ -548,22 +550,22 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>65.84999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="H3" s="1">
-        <v>34.15</v>
+        <v>33.3</v>
       </c>
       <c r="I3" s="2">
         <v>6.6</v>
@@ -580,10 +582,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -595,10 +597,10 @@
         <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>26.67</v>
+        <v>26.7</v>
       </c>
       <c r="H4" s="1">
-        <v>73.33</v>
+        <v>73.3</v>
       </c>
       <c r="I4" s="2">
         <v>5.5</v>
@@ -612,31 +614,25 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1">
-        <v>70.97</v>
+        <v>57.5</v>
       </c>
       <c r="H5" s="1">
-        <v>29.03</v>
+        <v>42.5</v>
       </c>
       <c r="I5" s="2">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -650,28 +646,28 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>80.48999999999999</v>
+        <v>71</v>
       </c>
       <c r="H6" s="1">
-        <v>19.51</v>
+        <v>29</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -685,28 +681,28 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>12.5</v>
-      </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -717,31 +713,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>88.37</v>
+        <v>87.5</v>
       </c>
       <c r="H8" s="1">
-        <v>11.63</v>
+        <v>12.5</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -752,31 +748,25 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G9" s="1">
-        <v>94.87</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>5.13</v>
+        <v>20.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -790,28 +780,28 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>85</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -825,28 +815,28 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
       <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="E11">
         <v>37</v>
       </c>
-      <c r="E11">
-        <v>31</v>
-      </c>
       <c r="F11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>83.78</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>16.22</v>
+        <v>5.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -857,36 +847,193 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>85</v>
+      </c>
+      <c r="H12" s="1">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>31</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1">
+        <v>83.8</v>
+      </c>
+      <c r="H13" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>159</v>
+      </c>
+      <c r="E14">
+        <v>140</v>
+      </c>
+      <c r="F14">
+        <v>19</v>
+      </c>
+      <c r="G14" s="1">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
         <v>33</v>
       </c>
-      <c r="E12">
+      <c r="E15">
         <v>31</v>
       </c>
-      <c r="F12">
+      <c r="F15">
         <v>2</v>
       </c>
-      <c r="G12" s="1">
-        <v>93.94</v>
-      </c>
-      <c r="H12" s="1">
-        <v>6.06</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="G15" s="1">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="I15" s="2">
         <v>8.4</v>
       </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>33</v>
+      </c>
+      <c r="E16">
+        <v>31</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>401</v>
+      </c>
+      <c r="E17">
+        <v>314</v>
+      </c>
+      <c r="F17">
+        <v>87</v>
+      </c>
+      <c r="G17" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="H17" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -897,11 +1044,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -947,31 +1094,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>26.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -982,28 +1132,31 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1011,63 +1164,63 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>73.3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>42.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.3</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1075,31 +1228,34 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>29</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1107,95 +1263,98 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1">
+        <v>80</v>
+      </c>
+      <c r="H7" s="1">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>100</v>
+      <c r="I7" s="2">
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>20.4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.1</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1203,31 +1362,34 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
       <c r="D10">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>11.6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1235,499 +1397,225 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
       <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="E11">
         <v>37</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
       <c r="F11">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>85</v>
+      </c>
+      <c r="H12" s="1">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>31</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1">
+        <v>83.8</v>
+      </c>
+      <c r="H13" s="1">
+        <v>16.2</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>159</v>
+      </c>
+      <c r="E14">
+        <v>140</v>
+      </c>
+      <c r="F14">
+        <v>19</v>
+      </c>
+      <c r="G14" s="1">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15">
         <v>33</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+      <c r="E15">
+        <v>31</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
         <v>33</v>
       </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>100</v>
-      </c>
-      <c r="J12">
-        <v>33</v>
-      </c>
-      <c r="K12" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="E16">
+        <v>31</v>
+      </c>
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="G16" s="1">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2">
-        <v>34</v>
-      </c>
-      <c r="E2">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1">
-        <v>73.53</v>
-      </c>
-      <c r="H2" s="1">
-        <v>26.47</v>
-      </c>
-      <c r="I2" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3">
-        <v>41</v>
-      </c>
-      <c r="E3">
-        <v>27</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1">
-        <v>65.84999999999999</v>
-      </c>
-      <c r="H3" s="1">
-        <v>34.15</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>22</v>
-      </c>
-      <c r="G4" s="1">
-        <v>26.67</v>
-      </c>
-      <c r="H4" s="1">
-        <v>73.33</v>
-      </c>
-      <c r="I4" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5">
-        <v>31</v>
-      </c>
-      <c r="E5">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5" s="1">
-        <v>70.97</v>
-      </c>
-      <c r="H5" s="1">
-        <v>29.03</v>
-      </c>
-      <c r="I5" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>41</v>
-      </c>
-      <c r="E6">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6" s="1">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="H6" s="1">
-        <v>19.51</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="I7" s="2">
-        <v>7.3</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>43</v>
-      </c>
-      <c r="E8">
-        <v>38</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1">
-        <v>88.37</v>
-      </c>
-      <c r="H8" s="1">
-        <v>11.63</v>
-      </c>
-      <c r="I8" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>37</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>94.87</v>
-      </c>
-      <c r="H9" s="1">
-        <v>5.13</v>
-      </c>
-      <c r="I9" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>34</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
-      </c>
-      <c r="G10" s="1">
-        <v>85</v>
-      </c>
-      <c r="H10" s="1">
-        <v>15</v>
-      </c>
-      <c r="I10" s="2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11">
-        <v>37</v>
-      </c>
-      <c r="E11">
-        <v>31</v>
-      </c>
-      <c r="F11">
-        <v>6</v>
-      </c>
-      <c r="G11" s="1">
-        <v>83.78</v>
-      </c>
-      <c r="H11" s="1">
-        <v>16.22</v>
-      </c>
-      <c r="I11" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12">
-        <v>33</v>
-      </c>
-      <c r="E12">
-        <v>31</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>93.94</v>
-      </c>
-      <c r="H12" s="1">
-        <v>6.06</v>
-      </c>
-      <c r="I12" s="2">
-        <v>8.4</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="D17">
+        <v>401</v>
+      </c>
+      <c r="E17">
+        <v>314</v>
+      </c>
+      <c r="F17">
+        <v>87</v>
+      </c>
+      <c r="G17" s="1">
+        <v>78.3</v>
+      </c>
+      <c r="H17" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="29">
   <si>
     <t>Docente</t>
   </si>
@@ -62,10 +62,13 @@
     <t>Saucedo Rivalcoba Graciela</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>LECTURA, EXPRESIÓN ORAL Y ESCRITA II</t>
+  </si>
+  <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>2AEM</t>
@@ -466,7 +469,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -512,10 +515,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>34</v>
@@ -547,10 +550,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>42</v>
@@ -582,10 +585,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -616,6 +619,9 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
       <c r="D5">
         <v>106</v>
       </c>
@@ -646,10 +652,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>31</v>
@@ -681,10 +687,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -716,10 +722,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -750,6 +756,9 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
       <c r="D9">
         <v>103</v>
       </c>
@@ -780,10 +789,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>43</v>
@@ -815,10 +824,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>39</v>
@@ -850,10 +859,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>40</v>
@@ -885,10 +894,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>37</v>
@@ -919,6 +928,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
       <c r="D14">
         <v>159</v>
       </c>
@@ -949,10 +961,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>33</v>
@@ -983,6 +995,9 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
       <c r="D16">
         <v>33</v>
       </c>
@@ -1008,9 +1023,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>15</v>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>17</v>
       </c>
       <c r="D17">
         <v>401</v>
@@ -1094,10 +1109,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>34</v>
@@ -1129,10 +1144,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>42</v>
@@ -1164,10 +1179,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -1198,6 +1213,9 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
       <c r="D5">
         <v>106</v>
       </c>
@@ -1228,10 +1246,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>31</v>
@@ -1263,10 +1281,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>40</v>
@@ -1298,10 +1316,10 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>32</v>
@@ -1332,6 +1350,9 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
       <c r="D9">
         <v>103</v>
       </c>
@@ -1362,10 +1383,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>43</v>
@@ -1397,10 +1418,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>39</v>
@@ -1432,10 +1453,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>40</v>
@@ -1467,10 +1488,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>37</v>
@@ -1501,6 +1522,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
       <c r="D14">
         <v>159</v>
       </c>
@@ -1531,10 +1555,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>33</v>
@@ -1565,6 +1589,9 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
       <c r="D16">
         <v>33</v>
       </c>
@@ -1590,9 +1617,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>15</v>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>17</v>
       </c>
       <c r="D17">
         <v>401</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="29">
   <si>
     <t>Docente</t>
   </si>
@@ -1118,6 +1119,600 @@
         <v>34</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>34</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>42</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>106</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>106</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>106</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>31</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>31</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>32</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>103</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>103</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>103</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>43</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>39</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>39</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>39</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>40</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13">
+        <v>37</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>37</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>37</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>159</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>159</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>100</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>159</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>33</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>33</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>33</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>33</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>33</v>
+      </c>
+      <c r="K16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <v>401</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>401</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>401</v>
+      </c>
+      <c r="K17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>34</v>
+      </c>
+      <c r="E2">
         <v>25</v>
       </c>
       <c r="F2">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -729,28 +729,28 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>28</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H8" s="1">
-        <v>12.5</v>
+        <v>15.2</v>
       </c>
       <c r="I8" s="2">
         <v>7.3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -761,28 +761,28 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9">
         <v>82</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H9" s="1">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
       <c r="I9" s="2">
         <v>7.1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1029,28 +1029,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E17">
         <v>314</v>
       </c>
       <c r="F17">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" s="1">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="I17" s="2">
         <v>7.4</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1323,13 +1323,13 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1355,13 +1355,13 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1623,13 +1623,13 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K17" s="1">
         <v>100</v>
@@ -1917,28 +1917,28 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>28</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>87.5</v>
+        <v>84.8</v>
       </c>
       <c r="H8" s="1">
-        <v>12.5</v>
+        <v>15.2</v>
       </c>
       <c r="I8" s="2">
         <v>7.3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1949,28 +1949,28 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E9">
         <v>82</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H9" s="1">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
       <c r="I9" s="2">
         <v>7.1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2217,28 +2217,28 @@
         <v>17</v>
       </c>
       <c r="D17">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E17">
         <v>314</v>
       </c>
       <c r="F17">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" s="1">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="I17" s="2">
         <v>7.4</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -1119,25 +1119,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>26.5</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1154,25 +1154,25 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1189,25 +1189,25 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1221,25 +1221,25 @@
         <v>106</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F5">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>34.9</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1393,25 +1393,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1463,25 +1463,25 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1498,25 +1498,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>10.8</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1530,25 +1530,25 @@
         <v>159</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F14">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>32.1</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1626,25 +1626,25 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F17">
-        <v>402</v>
+        <v>225</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J17">
-        <v>402</v>
+        <v>176</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>43.8</v>
       </c>
     </row>
   </sheetData>
@@ -1748,19 +1748,19 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="H3" s="1">
-        <v>33.3</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1783,19 +1783,19 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>26.7</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1">
-        <v>73.3</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1815,19 +1815,19 @@
         <v>106</v>
       </c>
       <c r="E5">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
-        <v>57.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>42.5</v>
+        <v>34.9</v>
       </c>
       <c r="I5" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1987,19 +1987,19 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>88.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="H10" s="1">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2057,19 +2057,19 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="H12" s="1">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2092,19 +2092,19 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>83.8</v>
+        <v>89.2</v>
       </c>
       <c r="H13" s="1">
-        <v>16.2</v>
+        <v>10.8</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2124,19 +2124,19 @@
         <v>159</v>
       </c>
       <c r="E14">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>88.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H14" s="1">
-        <v>11.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2220,19 +2220,19 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F17">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G17" s="1">
-        <v>78.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="H17" s="1">
-        <v>21.9</v>
+        <v>18.7</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>1</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -732,25 +732,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="I8" s="2">
         <v>7.3</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -764,25 +764,25 @@
         <v>104</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" s="1">
-        <v>78.8</v>
+        <v>79.8</v>
       </c>
       <c r="H9" s="1">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="I9" s="2">
         <v>7.1</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1032,25 +1032,25 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F17">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="1">
-        <v>78.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="I17" s="2">
         <v>7.4</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1256,25 +1256,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>58.1</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>41.9</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1291,25 +1291,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1326,25 +1326,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>12.1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1358,25 +1358,25 @@
         <v>104</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1428,25 +1428,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1530,25 +1530,25 @@
         <v>159</v>
       </c>
       <c r="E14">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F14">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>67.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H14" s="1">
-        <v>32.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" s="2">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="J14">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>24.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1626,25 +1626,25 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>177</v>
+        <v>292</v>
       </c>
       <c r="F17">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="G17" s="1">
-        <v>44</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>56</v>
+        <v>27.4</v>
       </c>
       <c r="I17" s="2">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="J17">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="K17" s="1">
-        <v>43.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1850,19 +1850,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>71</v>
+        <v>58.1</v>
       </c>
       <c r="H6" s="1">
-        <v>29</v>
+        <v>41.9</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1885,19 +1885,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="H7" s="1">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1920,25 +1920,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1952,25 +1952,25 @@
         <v>104</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1">
-        <v>78.8</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2034,7 +2034,7 @@
         <v>5.1</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2220,25 +2220,25 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F17">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G17" s="1">
-        <v>81.3</v>
+        <v>80.3</v>
       </c>
       <c r="H17" s="1">
-        <v>18.7</v>
+        <v>19.7</v>
       </c>
       <c r="I17" s="2">
         <v>7.6</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -1565,25 +1565,25 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1597,25 +1597,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11">
@@ -1626,25 +1626,25 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="F17">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="G17" s="1">
-        <v>72.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>27.4</v>
+        <v>19.9</v>
       </c>
       <c r="I17" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2159,19 +2159,19 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>93.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2191,19 +2191,19 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>93.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="I16" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2220,16 +2220,16 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F17">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" s="1">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="I17" s="2">
         <v>7.6</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -1063,8 +1063,7 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1657,8 +1656,7 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1713,19 +1711,19 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>73.5</v>
+        <v>85.3</v>
       </c>
       <c r="H2" s="1">
-        <v>26.5</v>
+        <v>14.7</v>
       </c>
       <c r="I2" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1748,19 +1746,19 @@
         <v>42</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>69</v>
+        <v>76.2</v>
       </c>
       <c r="H3" s="1">
-        <v>31</v>
+        <v>23.8</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1783,19 +1781,19 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>50</v>
+        <v>73.3</v>
       </c>
       <c r="H4" s="1">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="I4" s="2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1815,19 +1813,19 @@
         <v>106</v>
       </c>
       <c r="E5">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1">
-        <v>65.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="H5" s="1">
-        <v>34.9</v>
+        <v>21.7</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1850,19 +1848,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="H6" s="1">
-        <v>41.9</v>
+        <v>38.7</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1885,19 +1883,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1932,7 +1930,7 @@
         <v>12.1</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1964,7 +1962,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2159,19 +2157,19 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="I15" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2191,19 +2189,19 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="I16" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2220,19 +2218,19 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G17" s="1">
-        <v>80.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="H17" s="1">
-        <v>19.9</v>
+        <v>16.2</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20222.xlsx
@@ -1985,19 +1985,19 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>97.7</v>
+        <v>90.7</v>
       </c>
       <c r="H10" s="1">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>94.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>5.1</v>
+        <v>15.4</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2055,19 +2055,19 @@
         <v>40</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2090,19 +2090,19 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>89.2</v>
+        <v>75.7</v>
       </c>
       <c r="H13" s="1">
-        <v>10.8</v>
+        <v>24.3</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2122,19 +2122,19 @@
         <v>159</v>
       </c>
       <c r="E14">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1">
-        <v>91.2</v>
+        <v>83</v>
       </c>
       <c r="H14" s="1">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="I14" s="2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>402</v>
       </c>
       <c r="E17">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="F17">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G17" s="1">
-        <v>83.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>16.2</v>
+        <v>19.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
         <v>0</v>
